--- a/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
+++ b/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
@@ -13325,11 +13325,6 @@
           <t>1:50.150</t>
         </is>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>60130</t>
-        </is>
-      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>60129</t>
@@ -22755,11 +22750,6 @@
           <t>1:49.352</t>
         </is>
       </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>60130</t>
-        </is>
-      </c>
       <c r="U350" t="inlineStr">
         <is>
           <t>60129</t>
@@ -30217,11 +30207,6 @@
           <t>42395</t>
         </is>
       </c>
-      <c r="T466" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -35652,11 +35637,6 @@
           <t>42395</t>
         </is>
       </c>
-      <c r="T551" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -47350,11 +47330,6 @@
           <t>0:39.021</t>
         </is>
       </c>
-      <c r="R727" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -53719,11 +53694,6 @@
           <t>1:48.840</t>
         </is>
       </c>
-      <c r="R829" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
       <c r="S829" t="inlineStr">
         <is>
           <t>52171</t>
@@ -60059,11 +60029,6 @@
           <t>0:41.390</t>
         </is>
       </c>
-      <c r="R927" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
       <c r="S927" t="inlineStr">
         <is>
           <t>52171</t>
@@ -68558,11 +68523,6 @@
           <t>1:47.074</t>
         </is>
       </c>
-      <c r="R1062" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
       <c r="S1062" t="inlineStr">
         <is>
           <t>52171</t>
@@ -71978,11 +71938,6 @@
           <t>0:39.497</t>
         </is>
       </c>
-      <c r="R1115" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
       <c r="S1115" t="inlineStr">
         <is>
           <t>52171</t>
@@ -76445,11 +76400,6 @@
           <t>1:45.021</t>
         </is>
       </c>
-      <c r="R1184" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
       <c r="S1184" t="inlineStr">
         <is>
           <t>52171</t>
@@ -81891,11 +81841,6 @@
       <c r="P1267" t="inlineStr">
         <is>
           <t>0:39.640</t>
-        </is>
-      </c>
-      <c r="R1267" t="inlineStr">
-        <is>
-          <t>133041</t>
         </is>
       </c>
       <c r="S1267" t="inlineStr">
@@ -91670,7 +91615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D232"/>
+  <dimension ref="A1:D229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92072,17 +92017,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>46764</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scotty</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BICKNELL</t>
+          <t>BIRD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -92094,61 +92039,61 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>46764</t>
+          <t>126240</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Jana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BIRD</t>
+          <t>BLAHOVA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>42356</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jana</t>
+          <t>Nils Jensen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BLAHOVA</t>
+          <t>BOE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>42356</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nils Jensen</t>
+          <t>Maksim</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOE</t>
+          <t>BONDAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -92160,17 +92105,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>42454</t>
+          <t>52751</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maksim</t>
+          <t>Amin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BONDAR</t>
+          <t>BOUDAGHI</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -92182,17 +92127,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52751</t>
+          <t>35925</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amin</t>
+          <t>Bram</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BOUDAGHI</t>
+          <t>BRANDJES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -92204,17 +92149,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>35925</t>
+          <t>35698</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bram</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BRANDJES</t>
+          <t>BRENDEL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -92226,39 +92171,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>35698</t>
+          <t>52150</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Jo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BRENDEL</t>
+          <t>BRIGDEN-JONES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>52150</t>
+          <t>41678</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jo</t>
+          <t>Hannah</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BRIGDEN-JONES</t>
+          <t>BROWN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -92270,17 +92215,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>41678</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BROWN</t>
+          <t>BRUN-LIE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -92292,105 +92237,105 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BRUN-LIE</t>
+          <t>BRYANT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>42380</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Noemi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BRYANT</t>
+          <t>BRUSCHWEILER</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42380</t>
+          <t>35296</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Noemi</t>
+          <t>Guillaume</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BRUSCHWEILER</t>
+          <t>BURGER</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>35296</t>
+          <t>142729</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Guillaume</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BURGER</t>
+          <t>BURKE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>142729</t>
+          <t>36580</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BURKE</t>
+          <t>CAMPANA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -92402,83 +92347,83 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>36580</t>
+          <t>42729</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Gonzalo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CAMPANA</t>
+          <t>CARRERAS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>42729</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gonzalo</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CARRERAS</t>
+          <t>CARRINGTON</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>36405</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Miguel Angel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CARRINGTON</t>
+          <t>CASTANEDA CASTILLO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36405</t>
+          <t>36400</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Miguel Angel</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CASTANEDA CASTILLO</t>
+          <t>CASTANEDA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -92490,17 +92435,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>41785</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Olivier</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CASTANEDA</t>
+          <t>CAUWENBERGH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -92512,39 +92457,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>41785</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Olivier</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CAUWENBERGH</t>
+          <t>CAWTHORN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Ariela Cesar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CAWTHORN</t>
+          <t>PINTO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -92556,83 +92501,83 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>52294</t>
+          <t>46354</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ariela Cesar</t>
+          <t>Iurii</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PINTO</t>
+          <t>CHEBAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>46354</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Iurii</t>
+          <t>Stefania</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CHEBAN</t>
+          <t>CICALI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stefania</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CICALI</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>COCHRANE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -92644,39 +92589,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>73492</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Maria Cecilia</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>COCHRANE</t>
+          <t>COLLUEQUE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>73492</t>
+          <t>127568</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Maria Cecilia</t>
+          <t>Paula Maria</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>COLLUEQUE</t>
+          <t>RODRIGUEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -92688,39 +92633,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>127568</t>
+          <t>36587</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Paula Maria</t>
+          <t>Sergiu</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RODRIGUEZ FERNANDEZ</t>
+          <t>CRACIUN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sergiu</t>
+          <t>Saul</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CRACIUN</t>
+          <t>CRAVIOTTO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -92732,17 +92677,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>36045</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Saul</t>
+          <t>Francisco</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CRAVIOTTO</t>
+          <t>CUBELOS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -92754,17 +92699,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>36043</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Francisco</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CUBELOS</t>
+          <t>DANIELS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -92776,17 +92721,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Sergio</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DANIELS</t>
+          <t>DAVID DIAZ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -92798,17 +92743,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>60136</t>
+          <t>42732</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sergio</t>
+          <t>Juan Pablo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DAVID DIAZ</t>
+          <t>DE GESUS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -92820,17 +92765,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>42732</t>
+          <t>42450</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Juan Pablo</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DE GESUS</t>
+          <t>DE JONGE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -92842,17 +92787,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Erlon</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DE JONGE</t>
+          <t>DE SOUZA SILVA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -92864,17 +92809,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>36634</t>
+          <t>42731</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Erlon</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DE SOUZA SILVA</t>
+          <t>DE TORRES</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -92886,17 +92831,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>42731</t>
+          <t>36729</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Valentin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DE TORRES</t>
+          <t>DEMYANENKO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -92908,17 +92853,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>36729</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Valentin</t>
+          <t>Alexey</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DEMYANENKO</t>
+          <t>DERGUNOV</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -92930,17 +92875,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alexey</t>
+          <t>Miika</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DERGUNOV</t>
+          <t>DIETRICH</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -92952,61 +92897,61 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>35700</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Miika</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DIETRICH</t>
+          <t>DIETZE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>42477</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Igor</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DIETZE</t>
+          <t>DOROFEEV</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>42477</t>
+          <t>42452</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Igor</t>
+          <t>Philippe</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DOROFEEV</t>
+          <t>DUCHESNEAU</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -93018,17 +92963,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>42452</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Philippe</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DUCHESNEAU</t>
+          <t>DVORAK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -93040,17 +92985,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DVORAK</t>
+          <t>DYACHENKO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -93062,100 +93007,100 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>36002</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Edyta</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DYACHENKO</t>
+          <t>DZIENISZEWSKA KIERKLA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Edyta</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DZIENISZEWSKA KIERKLA</t>
+          <t>EGAN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Eliana</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EGAN</t>
+          <t>ESCALONA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>36503</t>
+          <t>63198</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eliana</t>
+          <t>Carlos Andres</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ESCALONA</t>
+          <t>ESCAMILLA OSPINA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>63198</t>
+          <t>63199</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Carlos Andres</t>
+          <t>Felipe</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -93172,83 +93117,83 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>63199</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Felipe</t>
+          <t>Ariel</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ESCAMILLA OSPINA</t>
+          <t>FARRAR-WELLMAN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>47792</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ariel</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FARRAR-WELLMAN</t>
+          <t>FITZGERALD</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>42173</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Naomi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FITZGERALD</t>
+          <t>FLOOD</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>42173</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Naomi</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FLOOD</t>
+          <t>FOURNEL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -93260,12 +93205,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>42455</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Hughes</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -93275,68 +93220,68 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>42455</t>
+          <t>65989</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hughes</t>
+          <t>Anastasia</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FOURNEL</t>
+          <t>GLININA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>65989</t>
+          <t>46418</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Anastasia</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GLININA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>46418</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GELLE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -93348,17 +93293,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>44434</t>
+          <t>42735</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Nelson Roberto</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GELLE</t>
+          <t>GERINGER SALLETE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -93370,17 +93315,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>42735</t>
+          <t>75776</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nelson Roberto</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GERINGER SALLETE</t>
+          <t>GOBLE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -93392,17 +93337,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>75776</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GOBLE</t>
+          <t>GOUBEL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -93414,17 +93359,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GOUBEL</t>
+          <t>GROSS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -93436,17 +93381,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Marcin</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GROSS</t>
+          <t>GRZYBOWSKI</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -93458,39 +93403,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GRZYBOWSKI</t>
+          <t>GUYOT</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>35924</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Eef</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GUYOT</t>
+          <t>HAAZE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -93502,39 +93447,39 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>35924</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Eef</t>
+          <t>Lubomir</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HAAZE</t>
+          <t>HAGARA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>64492</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lubomir</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HAGARA</t>
+          <t>HALL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -93546,39 +93491,39 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>64492</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HALL</t>
+          <t>HANNAH</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Henriette Engel</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HANNAH</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -93590,17 +93535,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Henriette Engel</t>
+          <t>Bridgitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>HARTLEY</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -93612,17 +93557,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bridgitte</t>
+          <t>Teneale</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HARTLEY</t>
+          <t>HATTON</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -93634,39 +93579,39 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Teneale</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HATTON</t>
+          <t>HAVEL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>35555</t>
+          <t>36048</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HAVEL</t>
+          <t>HERNANZ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -93678,17 +93623,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HERNANZ</t>
+          <t>HOFF</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -93700,61 +93645,61 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>42360</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HOFF</t>
+          <t>HOGAN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>42360</t>
+          <t>35708</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HOGAN</t>
+          <t>HOLLSTEIN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>42175</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Ervin</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HOLLSTEIN</t>
+          <t>HOLPERT</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -93766,17 +93711,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>42175</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ervin</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HOLPERT</t>
+          <t>HOLTZ</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -93788,61 +93733,61 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Jieyi</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HOLTZ</t>
+          <t>HUANG</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jieyi</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HUANG</t>
+          <t>INCOLLINGO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>36565</t>
+          <t>47312</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Edson Isaias</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>INCOLLINGO</t>
+          <t>FREITAS DA SILVA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -93854,61 +93799,61 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>47312</t>
+          <t>35325</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Edson Isaias</t>
+          <t>Lea</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FREITAS DA SILVA</t>
+          <t>JAMELOT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>35325</t>
+          <t>44435</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lea</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>JAMELOT</t>
+          <t>JANKOVEC</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>44435</t>
+          <t>36728</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Mirnazim</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JANKOVEC</t>
+          <t>JAVADOV</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -93920,17 +93865,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>36728</t>
+          <t>106229</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mirnazim</t>
+          <t>Jhonson</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JAVADOV</t>
+          <t>VERGARA MOLINA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -93942,39 +93887,39 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>106229</t>
+          <t>36502</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jhonson</t>
+          <t>Angelica</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VERGARA MOLINA</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36502</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Angelica</t>
+          <t>Karin</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>JOHANSSON</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -93986,17 +93931,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>49637</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Karin</t>
+          <t>Sofie Aastrand</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>JOHANSSON</t>
+          <t>JORGENSEN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -94008,39 +93953,39 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>49637</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sofie Aastrand</t>
+          <t>Sebastien</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JORGENSEN</t>
+          <t>JOUVE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sebastien</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>JOUVE</t>
+          <t>KACZOR</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -94052,17 +93997,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>35713</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KACZOR</t>
+          <t>KIRAJ</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -94074,39 +94019,39 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>118949</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Inna</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KIRAJ</t>
+          <t>KLINOVA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>118949</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Inna</t>
+          <t>Ivana</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>KLINOVA</t>
+          <t>KMETOVA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -94118,39 +94063,39 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ivana</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KMETOVA</t>
+          <t>KUJAWSKI</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KUJAWSKI</t>
+          <t>KULETA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -94162,17 +94107,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>130069</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Bohdan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>KULETA</t>
+          <t>KURUDZ</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -94184,17 +94129,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>130069</t>
+          <t>42348</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bohdan</t>
+          <t>Martin Trebbien Vestergaard</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KURUDZ</t>
+          <t>LARSEN</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -94206,17 +94151,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>42257</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Martin Trebbien Vestergaard</t>
+          <t>Andres</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LARSEN</t>
+          <t>LAZO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -94228,17 +94173,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>64070</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Andres</t>
+          <t>Tony Gill</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LAZO</t>
+          <t>LESPOIR</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -94250,17 +94195,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>64070</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Tony Gill</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>LESPOIR</t>
+          <t>LEUE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -94272,39 +94217,39 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>52169</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Zhangli</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LEUE</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>52169</t>
+          <t>52167</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Zhangli</t>
+          <t>Haiping</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LIU</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -94316,61 +94261,61 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>52167</t>
+          <t>46833</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Haiping</t>
+          <t>Emilio</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LIU</t>
+          <t>LLAMEDO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>36165</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Emilio</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LLAMEDO</t>
+          <t>LOBOVA</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Una Helen Bean</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LOBOVA</t>
+          <t>LOUNDER</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -94382,39 +94327,39 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Una Helen Bean</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LOUNDER</t>
+          <t>LOUW</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Kirill</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>LOUW</t>
+          <t>LUCHKIN</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -94426,83 +94371,83 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Kirill</t>
+          <t>Hayleigh-Jayne</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LUCHKIN</t>
+          <t>MASON</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>36635</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Hayleigh-Jayne</t>
+          <t>Ronilson Matias De</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MASON</t>
+          <t>OLIVEIRA</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>36635</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ronilson Matias De</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>OLIVEIRA</t>
+          <t>MATOUSKOVA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>42361</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Lucie</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MATOUSKOVA</t>
+          <t>MCELROY</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -94514,39 +94459,39 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>42361</t>
+          <t>36147</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Ilya</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MCELROY</t>
+          <t>MEDVEDEV</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>49430</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ilya</t>
+          <t>Emilio</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MEDVEDEV</t>
+          <t>MERCHAN</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -94558,17 +94503,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>49430</t>
+          <t>35721</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Emilio</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MERCHAN</t>
+          <t>MITTELSTEDT</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -94580,61 +94525,61 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>36412</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Maricela</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MITTELSTEDT</t>
+          <t>MONTEMAYOR RODRIGUEZ</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>36412</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Maricela</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MONTEMAYOR RODRIGUEZ</t>
+          <t>MORNEAU</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>42464</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MORNEAU</t>
+          <t>MORTIMER</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -94646,17 +94591,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>35394</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MORTIMER</t>
+          <t>MOUGET</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -94668,17 +94613,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>35394</t>
+          <t>42283</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Mohamed Ali</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MOUGET</t>
+          <t>MRABET</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -94690,39 +94635,39 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>42283</t>
+          <t>60129</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mohamed Ali</t>
+          <t>Tatiana</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MRABET</t>
+          <t>MUNOZ RUA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>60129</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Tatiana</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MUNOZ RUA</t>
+          <t>MURABITO</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -94734,83 +94679,83 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>36731</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Tamerlan</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MURABITO</t>
+          <t>MUSTAFAYEV</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>36731</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Tamerlan</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MUSTAFAYEV</t>
+          <t>NAJA</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>35557</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Ignas</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NAJA</t>
+          <t>NAVAKAUSKAS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ignas</t>
+          <t>Ricardas</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NAVAKAUSKAS</t>
+          <t>NEKRIOSIUS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -94822,61 +94767,61 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>45837</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ricardas</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NEKRIOSIUS</t>
+          <t>NICHOLLS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>NICHOLLS</t>
+          <t>NICOLAS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>61432</t>
+          <t>35723</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>NICOLAS</t>
+          <t>NUCK</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -94888,17 +94833,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>35723</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Mark William</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NUCK</t>
+          <t>OLDERSHAW</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -94910,17 +94855,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Mark William</t>
+          <t>Andrej</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>OLDERSHAW</t>
+          <t>OLIJNIK</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -94932,105 +94877,105 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Andrej</t>
+          <t>Genevieve Wendy Susan</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>OLIJNIK</t>
+          <t>ORTON</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>42467</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Genevieve Wendy Susan</t>
+          <t>Dejan</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ORTON</t>
+          <t>PAJIC</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dejan</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PAJIC</t>
+          <t>PALDANIUS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PALDANIUS</t>
+          <t>PANNECOUCKE</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PANNECOUCKE</t>
+          <t>PAROL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -95042,17 +94987,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>48494</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PAROL</t>
+          <t>PENDLE</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -95064,105 +95009,105 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>48494</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Cristina</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PENDLE</t>
+          <t>PETRACCA</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>42426</t>
+          <t>45847</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Cristina</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PETRACCA</t>
+          <t>PHILLIPS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>52610</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Irina</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PHILLIPS</t>
+          <t>PODOINIKOVA</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>60130</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Adriana</t>
+          <t>Vasily</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PITA NINO</t>
+          <t>POGREBAN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>52610</t>
+          <t>36598</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Irina</t>
+          <t>Pauliina</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PODOINIKOVA</t>
+          <t>POLET</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -95174,83 +95119,83 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>36150</t>
+          <t>65581</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Vasily</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>POGREBAN</t>
+          <t>PORTELA</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>36598</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Pauliina</t>
+          <t>Rene Holten</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>POLET</t>
+          <t>POULSEN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>65581</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PORTELA</t>
+          <t>PUTTO</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>36046</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Rene Holten</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>POULSEN</t>
+          <t>PEREZ RIAL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -95262,17 +95207,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>42767</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Isaquias</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PUTTO</t>
+          <t>GUIMARAES QUEIROZ</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -95284,17 +95229,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>36046</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Jaroslav</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PEREZ RIAL</t>
+          <t>RADON</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -95306,17 +95251,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>42767</t>
+          <t>75725</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Isaquias</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>GUIMARAES QUEIROZ</t>
+          <t>RAMELLA</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -95328,17 +95273,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>35549</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Jaroslav</t>
+          <t>Jose Giovanny</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>RADON</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -95350,17 +95295,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>75725</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>RAMELLA</t>
+          <t>RAUHE</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -95372,17 +95317,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Jose Giovanny</t>
+          <t>Brady Daniel Heim</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>REARDON</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -95394,17 +95339,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>35725</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>RAUHE</t>
+          <t>REBSTOCK</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -95416,17 +95361,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>36230</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Brady Daniel Heim</t>
+          <t>Kristian</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>REARDON</t>
+          <t>REEVES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -95438,105 +95383,105 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>52168</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Wenjun</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>REBSTOCK</t>
+          <t>REN</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>64706</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Kristian</t>
+          <t>Goviana</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>REEVES</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Wenjun</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>REN</t>
+          <t>RICCHETTI</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>64706</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Goviana</t>
+          <t>Maxime</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>RICHARD</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Nicola</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>RICCHETTI</t>
+          <t>RIPAMONTI</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -95548,17 +95493,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Maxime</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>RICHARD</t>
+          <t>ROSOLSKI</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -95570,17 +95515,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>36568</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Nicola</t>
+          <t>Aaron Joshua</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>RIPAMONTI</t>
+          <t>RUBLEE</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -95592,17 +95537,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Aleksejs</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ROSOLSKI</t>
+          <t>RUMJANCEVS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -95614,17 +95559,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>42481</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Aaron Joshua</t>
+          <t>Benjamin Rolph Mathew</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>RUBLEE</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -95636,39 +95581,39 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>52739</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Aleksejs</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>RUMJANCEVS</t>
+          <t>RUTISHAUSER</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>36148</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Benjamin Rolph Mathew</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>RYAKHOV</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -95680,39 +95625,39 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>36144</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Evgeny</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>RUTISHAUSER</t>
+          <t>SALAKHOV</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>36148</t>
+          <t>35981</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>RYAKHOV</t>
+          <t>SALBU</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -95724,61 +95669,61 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>73473</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Evgeny</t>
+          <t>Cornelia</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>SALAKHOV</t>
+          <t>SCHMIDT</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>SALBU</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>73473</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Cornelia</t>
+          <t>Viktoria</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SCHMIDT</t>
+          <t>SCHWARZ</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -95790,17 +95735,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Natalya</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>SERGEYEVA</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -95812,61 +95757,61 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>36792</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Viktoria</t>
+          <t>Jevgenij</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>SCHWARZ</t>
+          <t>SHUKLIN</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Natalya</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>SERGEYEVA</t>
+          <t>SIEMIONOWSKI</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Jevgenij</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SHUKLIN</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -95878,17 +95823,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>35980</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Jo Sondre</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>SIEMIONOWSKI</t>
+          <t>SOLHAUG</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -95900,17 +95845,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>42341</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Emil Staer</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>SIMENSEN</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -95922,17 +95867,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>35980</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Jo Sondre</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>SOLHAUG</t>
+          <t>STERBA</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -95944,17 +95889,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>42341</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Emil Staer</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>SIMENSEN</t>
+          <t>STEWART</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -95966,17 +95911,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>35776</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Kostja</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>STERBA</t>
+          <t>STROINSKI</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -95988,17 +95933,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>41591</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>STEWART</t>
+          <t>STYAN</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -96010,17 +95955,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>47627</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Kostja</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>STROINSKI</t>
+          <t>SVANQVIST</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -96032,17 +95977,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>STYAN</t>
+          <t>SVAB</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -96054,17 +95999,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>47627</t>
+          <t>47543</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Ahmadreza</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>SVANQVIST</t>
+          <t>TALEBIAN</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -96076,17 +96021,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Juraj</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SVAB</t>
+          <t>TARR</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -96098,17 +96043,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>47543</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ahmadreza</t>
+          <t>Alvaro</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>TALEBIAN</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -96120,39 +96065,39 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Juraj</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>TARR</t>
+          <t>TULEU</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>46419</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Alvaro</t>
+          <t>Quentin</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>URBAN</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -96164,39 +96109,39 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>TULEU</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>42493</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Quentin</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>URBAN</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -96208,17 +96153,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Anton</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>VASILYEV</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -96230,39 +96175,39 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Roland</t>
+          <t>Oona</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>VASKO</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>35729</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Anton</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>VASILYEV</t>
+          <t>VERCH</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -96274,17 +96219,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>42770</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Oona</t>
+          <t>Ana Paula</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>VASKO</t>
+          <t>VERGUTZ</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -96296,61 +96241,61 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>35729</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Laurence</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>VERCH</t>
+          <t>VINCENT-LAPOINTE</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>42770</t>
+          <t>45725</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Ana Paula</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>VERGUTZ</t>
+          <t>VLCEK</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Laurence</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>VINCENT-LAPOINTE</t>
+          <t>WALCZYKIEWICZ</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -96362,39 +96307,39 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>45725</t>
+          <t>36222</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>VLCEK</t>
+          <t>WALKER</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Conny</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>WALCZYKIEWICZ</t>
+          <t>WASSMUTH</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -96406,39 +96351,39 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>36222</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>WALKER</t>
+          <t>WATKINS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Conny</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>WASSMUTH</t>
+          <t>WOJNAROWSKA</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -96450,83 +96395,83 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>52171</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Yanan</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>WATKINS</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>WOJNAROWSKA</t>
+          <t>WYLENZEK</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>52171</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Yanan</t>
+          <t>Fabio</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>WYSS</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>61026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Haitao</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>WYLENZEK</t>
+          <t>XU</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -96538,17 +96483,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>36149</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Fabio</t>
+          <t>Vitaly</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>WYSS</t>
+          <t>YURCHENKO</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -96560,17 +96505,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Haitao</t>
+          <t>Jost</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>XU</t>
+          <t>ZAKRAJSEK</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -96582,39 +96527,39 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>64705</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Vitaly</t>
+          <t>Fabiola</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>YURCHENKO</t>
+          <t>ZAMORANO</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>36310</t>
+          <t>36152</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Jost</t>
+          <t>Oleg</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ZAKRAJSEK</t>
+          <t>ZHESTKOV</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -96626,39 +96571,39 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>64705</t>
+          <t>60015</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Fabiola</t>
+          <t>Peng</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ZAMORANO</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>133041</t>
+          <t>52182</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Hong</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ZHANG</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -96670,17 +96615,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>36152</t>
+          <t>61025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Oleg</t>
+          <t>Yubo</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ZHESTKOV</t>
+          <t>ZHOU</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -96692,86 +96637,20 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>60015</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Peng</t>
+          <t>Milenko</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ZHOU</t>
+          <t>ZORIC</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>52182</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Yu</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>ZHOU</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>61025</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Yubo</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>ZHOU</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>42179</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Milenko</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>ZORIC</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
+++ b/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
@@ -5238,6 +5238,11 @@
           <t>4:09.431</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>64983</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5863,6 +5868,11 @@
           <t>3:37.970</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6178,6 +6188,11 @@
           <t>3:47.742</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6870,6 +6885,11 @@
           <t>3:48.940</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7245,6 +7265,11 @@
           <t>4:08.674</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7815,6 +7840,11 @@
           <t>4:06.000</t>
         </is>
       </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7995,6 +8025,11 @@
           <t>4:21.040</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8610,6 +8645,11 @@
           <t>4:40.229</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9580,6 +9620,11 @@
           <t>3:41.377</t>
         </is>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10360,6 +10405,11 @@
           <t>3:33.242</t>
         </is>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11245,6 +11295,11 @@
           <t>3:28.343</t>
         </is>
       </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11890,6 +11945,11 @@
           <t>49430</t>
         </is>
       </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -17100,6 +17160,11 @@
           <t>4:09.246</t>
         </is>
       </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -17160,6 +17225,11 @@
           <t>3:34.006</t>
         </is>
       </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -18600,6 +18670,11 @@
           <t>4:09.977</t>
         </is>
       </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -18910,6 +18985,11 @@
           <t>4:02.632</t>
         </is>
       </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -21290,6 +21370,11 @@
           <t>49430</t>
         </is>
       </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -21540,6 +21625,11 @@
           <t>3:37.681</t>
         </is>
       </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -23935,6 +24025,11 @@
           <t>1:47.374</t>
         </is>
       </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -24925,6 +25020,11 @@
           <t>1:48.800</t>
         </is>
       </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -25875,6 +25975,11 @@
           <t>1:57.892</t>
         </is>
       </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -26555,6 +26660,11 @@
           <t>2:18.105</t>
         </is>
       </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -27317,6 +27427,11 @@
           <t>1:41.558</t>
         </is>
       </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -27572,6 +27687,11 @@
           <t>1:44.782</t>
         </is>
       </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -27967,6 +28087,11 @@
           <t>49430</t>
         </is>
       </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -28342,6 +28467,11 @@
           <t>1:50.346</t>
         </is>
       </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -28797,6 +28927,11 @@
           <t>1:50.215</t>
         </is>
       </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -29607,6 +29742,11 @@
           <t>42727</t>
         </is>
       </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>42724</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -30082,6 +30222,11 @@
           <t>36231</t>
         </is>
       </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -30142,6 +30287,16 @@
           <t>3:19.550</t>
         </is>
       </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>46830</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>46829</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -30202,6 +30357,11 @@
           <t>3:37.829</t>
         </is>
       </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>64983</t>
+        </is>
+      </c>
       <c r="S466" t="inlineStr">
         <is>
           <t>42395</t>
@@ -30417,6 +30577,11 @@
           <t>3:12.425</t>
         </is>
       </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -30877,6 +31042,11 @@
           <t>1:50.367</t>
         </is>
       </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -31942,6 +32112,11 @@
           <t>1:46.779</t>
         </is>
       </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -33437,6 +33612,11 @@
           <t>2:25.077</t>
         </is>
       </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -33567,6 +33747,11 @@
           <t>49430</t>
         </is>
       </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -33947,6 +34132,11 @@
           <t>1:49.127</t>
         </is>
       </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -34582,6 +34772,11 @@
           <t>1:46.846</t>
         </is>
       </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -35167,6 +35362,11 @@
           <t>3:09.134</t>
         </is>
       </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -35437,6 +35637,11 @@
           <t>36231</t>
         </is>
       </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -35632,6 +35837,11 @@
           <t>3:17.451</t>
         </is>
       </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>64983</t>
+        </is>
+      </c>
       <c r="S551" t="inlineStr">
         <is>
           <t>42395</t>
@@ -35712,6 +35922,11 @@
           <t>42727</t>
         </is>
       </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>42724</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -35922,6 +36137,16 @@
           <t>3:04.310</t>
         </is>
       </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>46830</t>
+        </is>
+      </c>
+      <c r="T555" t="inlineStr">
+        <is>
+          <t>46829</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -37863,6 +38088,11 @@
           <t>4:00.328</t>
         </is>
       </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -39218,6 +39448,11 @@
           <t>49430</t>
         </is>
       </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -40141,6 +40376,11 @@
           <t>36231</t>
         </is>
       </c>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -42193,6 +42433,11 @@
           <t>3:34.508</t>
         </is>
       </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -42518,6 +42763,11 @@
           <t>3:54.899</t>
         </is>
       </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -44101,6 +44351,11 @@
           <t>3:33.629</t>
         </is>
       </c>
+      <c r="S678" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -45627,6 +45882,11 @@
           <t>2:55.161</t>
         </is>
       </c>
+      <c r="U700" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -45689,6 +45949,16 @@
           <t>2:55.897</t>
         </is>
       </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>46830</t>
+        </is>
+      </c>
+      <c r="T701" t="inlineStr">
+        <is>
+          <t>46829</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -45965,6 +46235,11 @@
           <t>0:36.514</t>
         </is>
       </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>42262</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -46645,6 +46920,11 @@
           <t>0:37.503</t>
         </is>
       </c>
+      <c r="R716" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -47205,6 +47485,11 @@
           <t>0:37.719</t>
         </is>
       </c>
+      <c r="R725" t="inlineStr">
+        <is>
+          <t>70070</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -51764,6 +52049,11 @@
           <t>0:42.368</t>
         </is>
       </c>
+      <c r="R798" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -52329,6 +52619,11 @@
           <t>0:44.588</t>
         </is>
       </c>
+      <c r="R807" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -52509,6 +52804,11 @@
           <t>0:39.290</t>
         </is>
       </c>
+      <c r="R810" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -53309,6 +53609,11 @@
           <t>0:44.146</t>
         </is>
       </c>
+      <c r="R823" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -53824,6 +54129,11 @@
           <t>1:50.370</t>
         </is>
       </c>
+      <c r="S831" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -57309,6 +57619,11 @@
           <t>0:34.396</t>
         </is>
       </c>
+      <c r="S885" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -57369,6 +57684,11 @@
           <t>0:34.835</t>
         </is>
       </c>
+      <c r="S886" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -59124,6 +59444,11 @@
           <t>0:37.971</t>
         </is>
       </c>
+      <c r="S913" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -59589,6 +59914,11 @@
           <t>0:38.944</t>
         </is>
       </c>
+      <c r="R920" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -60599,6 +60929,11 @@
           <t>0:36.663</t>
         </is>
       </c>
+      <c r="R936" t="inlineStr">
+        <is>
+          <t>42262</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -60784,6 +61119,11 @@
           <t>0:37.946</t>
         </is>
       </c>
+      <c r="R939" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
@@ -62414,6 +62754,11 @@
           <t>0:37.302</t>
         </is>
       </c>
+      <c r="R965" t="inlineStr">
+        <is>
+          <t>70070</t>
+        </is>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -65421,6 +65766,11 @@
           <t>0:46.194</t>
         </is>
       </c>
+      <c r="R1013" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
@@ -65851,6 +66201,11 @@
           <t>0:43.171</t>
         </is>
       </c>
+      <c r="R1020" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
@@ -66036,6 +66391,11 @@
           <t>0:40.389</t>
         </is>
       </c>
+      <c r="R1023" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
@@ -66411,6 +66771,11 @@
           <t>0:42.783</t>
         </is>
       </c>
+      <c r="R1029" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
@@ -68588,6 +68953,11 @@
           <t>1:50.229</t>
         </is>
       </c>
+      <c r="S1063" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
@@ -69608,6 +69978,11 @@
           <t>0:34.202</t>
         </is>
       </c>
+      <c r="S1079" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
@@ -69993,6 +70368,11 @@
           <t>0:38.869</t>
         </is>
       </c>
+      <c r="R1085" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
@@ -70773,6 +71153,11 @@
           <t>0:34.507</t>
         </is>
       </c>
+      <c r="S1097" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
@@ -73232,6 +73617,11 @@
           <t>0:36.922</t>
         </is>
       </c>
+      <c r="R1135" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
@@ -73294,6 +73684,11 @@
           <t>0:36.933</t>
         </is>
       </c>
+      <c r="R1136" t="inlineStr">
+        <is>
+          <t>70070</t>
+        </is>
+      </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
@@ -73480,6 +73875,11 @@
           <t>0:35.496</t>
         </is>
       </c>
+      <c r="R1139" t="inlineStr">
+        <is>
+          <t>42262</t>
+        </is>
+      </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
@@ -75998,6 +76398,11 @@
           <t>1:48.686</t>
         </is>
       </c>
+      <c r="S1178" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
@@ -77663,6 +78068,11 @@
           <t>0:34.278</t>
         </is>
       </c>
+      <c r="S1203" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
@@ -77725,6 +78135,11 @@
           <t>0:34.292</t>
         </is>
       </c>
+      <c r="S1204" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
@@ -79625,6 +80040,11 @@
           <t>0:39.918</t>
         </is>
       </c>
+      <c r="R1233" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
@@ -82034,6 +82454,11 @@
           <t>0:36.768</t>
         </is>
       </c>
+      <c r="R1270" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
@@ -82096,6 +82521,11 @@
           <t>0:36.784</t>
         </is>
       </c>
+      <c r="S1271" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
@@ -82766,6 +83196,11 @@
           <t>1:37.993</t>
         </is>
       </c>
+      <c r="R1281" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
@@ -83153,6 +83588,11 @@
           <t>1:44.560</t>
         </is>
       </c>
+      <c r="R1287" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
@@ -85711,6 +86151,11 @@
           <t>1:49.720</t>
         </is>
       </c>
+      <c r="R1326" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
@@ -86443,6 +86888,11 @@
           <t>49430</t>
         </is>
       </c>
+      <c r="S1337" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
@@ -86902,6 +87352,11 @@
           <t>1:38.020</t>
         </is>
       </c>
+      <c r="S1344" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
@@ -86964,6 +87419,11 @@
           <t>1:38.087</t>
         </is>
       </c>
+      <c r="S1345" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
@@ -87716,6 +88176,11 @@
           <t>2:33.363</t>
         </is>
       </c>
+      <c r="T1356" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
@@ -88150,6 +88615,11 @@
           <t>36046</t>
         </is>
       </c>
+      <c r="S1362" t="inlineStr">
+        <is>
+          <t>70070</t>
+        </is>
+      </c>
       <c r="U1362" t="inlineStr">
         <is>
           <t>36045</t>
@@ -88361,6 +88831,11 @@
           <t>2:36.206</t>
         </is>
       </c>
+      <c r="T1365" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
@@ -88634,6 +89109,11 @@
           <t>2:43.533</t>
         </is>
       </c>
+      <c r="R1369" t="inlineStr">
+        <is>
+          <t>42724</t>
+        </is>
+      </c>
       <c r="S1369" t="inlineStr">
         <is>
           <t>42731</t>
@@ -88642,6 +89122,11 @@
       <c r="T1369" t="inlineStr">
         <is>
           <t>42729</t>
+        </is>
+      </c>
+      <c r="U1369" t="inlineStr">
+        <is>
+          <t>42725</t>
         </is>
       </c>
     </row>
@@ -90536,6 +91021,11 @@
           <t>36046</t>
         </is>
       </c>
+      <c r="S1395" t="inlineStr">
+        <is>
+          <t>70070</t>
+        </is>
+      </c>
       <c r="U1395" t="inlineStr">
         <is>
           <t>36045</t>
@@ -90896,6 +91386,11 @@
           <t>2:30.991</t>
         </is>
       </c>
+      <c r="T1400" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
@@ -91177,6 +91672,16 @@
       <c r="P1404" t="inlineStr">
         <is>
           <t>2:53.089</t>
+        </is>
+      </c>
+      <c r="S1404" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
+      <c r="U1404" t="inlineStr">
+        <is>
+          <t>36155</t>
         </is>
       </c>
     </row>
@@ -91615,7 +92120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D229"/>
+  <dimension ref="A1:D253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96656,6 +97161,534 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>36049</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>COSGAYA</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ANOSHKIN</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>36159</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Ilia</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SHTOKALOV</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Viktor</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>MELANTEV</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>BOYTON</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Ronny</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>RATIA</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>42262</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>DE CESARE</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>PRA FLORIANI</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>MEHAK</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>42724</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>DAL BO</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>42725</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>CORREA</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>46407</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Vitalii</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>TSURKAN</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>46829</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>GERMADE</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>46830</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Inigo</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>PENA</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>47311</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Gilvan</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>BITTENCOURT RIBEIRO</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Shahou</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>NASERI</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>HEFNER</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>64983</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Zac</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>FRANICH</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>69144</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Lissa</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>BISSONNETTE</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>70070</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>ANDRES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>106349</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Saeid</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>FAZLOULA</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
+++ b/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
@@ -13385,6 +13385,11 @@
           <t>1:50.150</t>
         </is>
       </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>60130</t>
+        </is>
+      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>60129</t>
@@ -22840,6 +22845,11 @@
           <t>1:49.352</t>
         </is>
       </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>60130</t>
+        </is>
+      </c>
       <c r="U350" t="inlineStr">
         <is>
           <t>60129</t>
@@ -30367,6 +30377,11 @@
           <t>42395</t>
         </is>
       </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -35847,6 +35862,11 @@
           <t>42395</t>
         </is>
       </c>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -47615,6 +47635,11 @@
           <t>0:39.021</t>
         </is>
       </c>
+      <c r="R727" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -53999,6 +54024,11 @@
           <t>1:48.840</t>
         </is>
       </c>
+      <c r="R829" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
       <c r="S829" t="inlineStr">
         <is>
           <t>52171</t>
@@ -60359,6 +60389,11 @@
           <t>0:41.390</t>
         </is>
       </c>
+      <c r="R927" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
       <c r="S927" t="inlineStr">
         <is>
           <t>52171</t>
@@ -68888,6 +68923,11 @@
           <t>1:47.074</t>
         </is>
       </c>
+      <c r="R1062" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
       <c r="S1062" t="inlineStr">
         <is>
           <t>52171</t>
@@ -72323,6 +72363,11 @@
           <t>0:39.497</t>
         </is>
       </c>
+      <c r="R1115" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
       <c r="S1115" t="inlineStr">
         <is>
           <t>52171</t>
@@ -76805,6 +76850,11 @@
           <t>1:45.021</t>
         </is>
       </c>
+      <c r="R1184" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
       <c r="S1184" t="inlineStr">
         <is>
           <t>52171</t>
@@ -82261,6 +82311,11 @@
       <c r="P1267" t="inlineStr">
         <is>
           <t>0:39.640</t>
+        </is>
+      </c>
+      <c r="R1267" t="inlineStr">
+        <is>
+          <t>133041</t>
         </is>
       </c>
       <c r="S1267" t="inlineStr">
@@ -92120,7 +92175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D253"/>
+  <dimension ref="A1:D256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97689,6 +97744,72 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Scotty</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>BICKNELL</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>60130</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Adriana</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>PITA NINO</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>133041</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Hong</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>ZHANG</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
+++ b/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
@@ -13385,11 +13385,6 @@
           <t>1:50.150</t>
         </is>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>60130</t>
-        </is>
-      </c>
       <c r="U202" t="inlineStr">
         <is>
           <t>60129</t>
@@ -22845,11 +22840,6 @@
           <t>1:49.352</t>
         </is>
       </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>60130</t>
-        </is>
-      </c>
       <c r="U350" t="inlineStr">
         <is>
           <t>60129</t>
@@ -30377,11 +30367,6 @@
           <t>42395</t>
         </is>
       </c>
-      <c r="T466" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -35862,11 +35847,6 @@
           <t>42395</t>
         </is>
       </c>
-      <c r="T551" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -47635,11 +47615,6 @@
           <t>0:39.021</t>
         </is>
       </c>
-      <c r="R727" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -54024,11 +53999,6 @@
           <t>1:48.840</t>
         </is>
       </c>
-      <c r="R829" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
       <c r="S829" t="inlineStr">
         <is>
           <t>52171</t>
@@ -60389,11 +60359,6 @@
           <t>0:41.390</t>
         </is>
       </c>
-      <c r="R927" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
       <c r="S927" t="inlineStr">
         <is>
           <t>52171</t>
@@ -68923,11 +68888,6 @@
           <t>1:47.074</t>
         </is>
       </c>
-      <c r="R1062" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
       <c r="S1062" t="inlineStr">
         <is>
           <t>52171</t>
@@ -72363,11 +72323,6 @@
           <t>0:39.497</t>
         </is>
       </c>
-      <c r="R1115" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
       <c r="S1115" t="inlineStr">
         <is>
           <t>52171</t>
@@ -76850,11 +76805,6 @@
           <t>1:45.021</t>
         </is>
       </c>
-      <c r="R1184" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
       <c r="S1184" t="inlineStr">
         <is>
           <t>52171</t>
@@ -82311,11 +82261,6 @@
       <c r="P1267" t="inlineStr">
         <is>
           <t>0:39.640</t>
-        </is>
-      </c>
-      <c r="R1267" t="inlineStr">
-        <is>
-          <t>133041</t>
         </is>
       </c>
       <c r="S1267" t="inlineStr">
@@ -92175,7 +92120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D256"/>
+  <dimension ref="A1:D253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97744,72 +97689,6 @@
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Scotty</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>BICKNELL</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>60130</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Adriana</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>PITA NINO</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>133041</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Hong</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>ZHANG</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
+++ b/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
@@ -3443,6 +3443,11 @@
           <t>1:59.304</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14975,6 +14980,11 @@
           <t>2:03.570</t>
         </is>
       </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -56004,6 +56014,11 @@
           <t>73492</t>
         </is>
       </c>
+      <c r="S860" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -68563,6 +68578,11 @@
           <t>73492</t>
         </is>
       </c>
+      <c r="S1057" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" t="inlineStr">
@@ -76674,6 +76694,11 @@
       <c r="R1182" t="inlineStr">
         <is>
           <t>73492</t>
+        </is>
+      </c>
+      <c r="S1182" t="inlineStr">
+        <is>
+          <t>47909</t>
         </is>
       </c>
     </row>
@@ -92120,7 +92145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D253"/>
+  <dimension ref="A1:D254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97689,6 +97714,28 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>47909</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Alexandra Borbala</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>KEREZTESI</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
+++ b/events/Duisburg_2011_WC/Duisburg_2011_WC_Results.xlsx
@@ -51809,6 +51809,11 @@
           <t>0:40.439</t>
         </is>
       </c>
+      <c r="R794" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -66471,6 +66476,11 @@
           <t>0:41.236</t>
         </is>
       </c>
+      <c r="R1024" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
@@ -80455,6 +80465,11 @@
       <c r="P1239" t="inlineStr">
         <is>
           <t>0:40.930</t>
+        </is>
+      </c>
+      <c r="R1239" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
     </row>
@@ -92145,7 +92160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D254"/>
+  <dimension ref="A1:D255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97736,6 +97751,28 @@
         </is>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Nivalter</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Santos de Jesus</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
